--- a/Riverside_Cost_Tracker.xlsx
+++ b/Riverside_Cost_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ajaysingh/Library/Application Support/Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA74617-3931-084A-B536-309BCCE16A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D45BF4-2DB0-574F-94AC-ED6F169D225F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="7" xr2:uid="{8B75C85C-4101-1946-9BF4-708ABAF51156}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="5" xr2:uid="{8B75C85C-4101-1946-9BF4-708ABAF51156}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Info" sheetId="1" r:id="rId1"/>
@@ -228,9 +228,6 @@
     <t>Approved</t>
   </si>
   <si>
-    <t>Project Sponser</t>
-  </si>
-  <si>
     <t>CR002</t>
   </si>
   <si>
@@ -394,6 +391,9 @@
   </si>
   <si>
     <t>Forecast</t>
+  </si>
+  <si>
+    <t>Project Sponsor</t>
   </si>
 </sst>
 </file>
@@ -466,7 +466,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -491,10 +491,6 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -672,7 +668,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-GB"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2885,10 +2881,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -5476,125 +5468,123 @@
   <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.6640625" style="17" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" style="17" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="17"/>
-    <col min="4" max="4" width="19.83203125" style="17" customWidth="1"/>
-    <col min="5" max="5" width="43.5" style="17" customWidth="1"/>
-    <col min="6" max="6" width="17.83203125" style="17" customWidth="1"/>
-    <col min="7" max="7" width="16" style="17" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" style="17" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" style="17" customWidth="1"/>
-    <col min="10" max="10" width="15.5" style="17" customWidth="1"/>
-    <col min="11" max="16384" width="10.83203125" style="17"/>
+    <col min="1" max="1" width="23.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" customWidth="1"/>
+    <col min="4" max="4" width="19.83203125" customWidth="1"/>
+    <col min="5" max="5" width="43.5" customWidth="1"/>
+    <col min="6" max="6" width="17.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="17" t="s">
+      <c r="A3" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" t="s">
         <v>43</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I3" t="s">
         <v>53</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="J3" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
+      <c r="A4" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="15">
         <v>46188</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="17" t="str">
+      <c r="D4" t="str">
         <f>_xlfn.XLOOKUP(C4, Budget!$A$4:$A$9, Budget!$B$4:$B$9, "Not Found")</f>
         <v>Enabling Works</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" t="s">
         <v>56</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" t="s">
         <v>57</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="11">
         <v>35000</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" t="s">
         <v>58</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="I4" t="s">
+        <v>114</v>
+      </c>
+      <c r="J4" s="15">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>59</v>
       </c>
-      <c r="J4" s="18">
-        <v>46203</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" s="18">
+      <c r="B5" s="15">
         <v>46254</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="17" t="str">
+      <c r="D5" t="str">
         <f>_xlfn.XLOOKUP(C5, Budget!$A$4:$A$9, Budget!$B$4:$B$9, "Not Found")</f>
         <v>Design and Surveys</v>
       </c>
       <c r="E5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" t="s">
         <v>61</v>
       </c>
-      <c r="F5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G5" s="19">
+      <c r="G5" s="11">
         <v>25000</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" t="s">
         <v>58</v>
       </c>
-      <c r="I5" s="17" t="s">
-        <v>59</v>
+      <c r="I5" t="s">
+        <v>114</v>
       </c>
       <c r="J5" s="15">
         <v>46270</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="17" t="s">
-        <v>63</v>
+      <c r="A6" t="s">
+        <v>62</v>
       </c>
       <c r="B6" s="15">
         <v>46290</v>
@@ -5602,26 +5592,26 @@
       <c r="C6" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="17" t="str">
+      <c r="D6" t="str">
         <f>_xlfn.XLOOKUP(C6, Budget!$A$4:$A$9, Budget!$B$4:$B$9, "Not Found")</f>
         <v>Civils and Structures</v>
       </c>
       <c r="E6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" t="s">
         <v>64</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" s="11">
+        <v>20000</v>
+      </c>
+      <c r="H6" t="s">
         <v>65</v>
-      </c>
-      <c r="G6" s="19">
-        <v>20000</v>
-      </c>
-      <c r="H6" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B9" s="13">
         <f>Budget!O10</f>
@@ -5630,7 +5620,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B10" s="13">
         <f>SUMIFS(G4:G20,H4:H20,"Approved")</f>
@@ -5639,7 +5629,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B11" s="13">
         <f>B9+B10</f>
@@ -5657,7 +5647,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B13" s="13">
         <f>B11-B12</f>
@@ -5666,7 +5656,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B14" s="13">
         <f>SUMIFS(G4:G20,H4:H20,"Proposed")</f>
@@ -5695,19 +5685,19 @@
     <col min="7" max="7" width="15" customWidth="1"/>
     <col min="8" max="8" width="12.6640625" customWidth="1"/>
     <col min="11" max="11" width="17.1640625" style="6" customWidth="1"/>
-    <col min="12" max="12" width="10.83203125" style="21"/>
+    <col min="12" max="12" width="10.83203125" style="17"/>
     <col min="13" max="13" width="17.5" style="6" customWidth="1"/>
     <col min="14" max="14" width="41.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
@@ -5722,31 +5712,31 @@
         <v>50</v>
       </c>
       <c r="F3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" t="s">
         <v>74</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>75</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>76</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>77</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="L3" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="L3" s="21" t="s">
+      <c r="M3" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="N3" t="s">
         <v>81</v>
-      </c>
-      <c r="N3" t="s">
-        <v>82</v>
       </c>
       <c r="O3" t="s">
         <v>43</v>
@@ -5754,7 +5744,7 @@
     </row>
     <row r="4" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B4" s="15">
         <v>46266</v>
@@ -5767,10 +5757,10 @@
         <v>Civils and Structures</v>
       </c>
       <c r="E4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -5782,14 +5772,14 @@
         <f>G4*H4</f>
         <v>16</v>
       </c>
-      <c r="J4" s="20" t="str">
+      <c r="J4" s="16" t="str">
         <f>IF(I4&gt;=15,"High",IF(I4&gt;=8,"Medium","Low"))</f>
         <v>High</v>
       </c>
       <c r="K4" s="6">
         <v>60000</v>
       </c>
-      <c r="L4" s="21">
+      <c r="L4" s="17">
         <v>0.5</v>
       </c>
       <c r="M4" s="6">
@@ -5797,15 +5787,15 @@
         <v>30000</v>
       </c>
       <c r="N4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B5" s="15">
         <v>46270</v>
@@ -5818,10 +5808,10 @@
         <v>Mechanical and Electrical</v>
       </c>
       <c r="E5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -5833,14 +5823,14 @@
         <f t="shared" ref="I5:I8" si="0">G5*H5</f>
         <v>12</v>
       </c>
-      <c r="J5" s="20" t="str">
+      <c r="J5" s="16" t="str">
         <f t="shared" ref="J5:J8" si="1">IF(I5&gt;=15,"High",IF(I5&gt;=8,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
       <c r="K5" s="6">
         <v>40000</v>
       </c>
-      <c r="L5" s="21">
+      <c r="L5" s="17">
         <v>0.4</v>
       </c>
       <c r="M5" s="6">
@@ -5848,15 +5838,15 @@
         <v>16000</v>
       </c>
       <c r="N5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B6" s="15">
         <v>46275</v>
@@ -5869,10 +5859,10 @@
         <v>Fit-out and Finishes</v>
       </c>
       <c r="E6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -5884,14 +5874,14 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="J6" s="20" t="str">
+      <c r="J6" s="16" t="str">
         <f t="shared" si="1"/>
         <v>Medium</v>
       </c>
       <c r="K6" s="6">
         <v>30000</v>
       </c>
-      <c r="L6" s="21">
+      <c r="L6" s="17">
         <v>0.3</v>
       </c>
       <c r="M6" s="6">
@@ -5899,15 +5889,15 @@
         <v>9000</v>
       </c>
       <c r="N6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B7" s="15">
         <v>46280</v>
@@ -5920,10 +5910,10 @@
         <v>Testing and Handover</v>
       </c>
       <c r="E7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -5935,14 +5925,14 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="J7" s="20" t="str">
+      <c r="J7" s="16" t="str">
         <f t="shared" si="1"/>
         <v>Medium</v>
       </c>
       <c r="K7" s="6">
         <v>50000</v>
       </c>
-      <c r="L7" s="21">
+      <c r="L7" s="17">
         <v>0.2</v>
       </c>
       <c r="M7" s="6">
@@ -5950,15 +5940,15 @@
         <v>10000</v>
       </c>
       <c r="N7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B8" s="15">
         <v>46143</v>
@@ -5971,10 +5961,10 @@
         <v>Enabling Works</v>
       </c>
       <c r="E8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -5986,14 +5976,14 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="J8" s="20" t="str">
+      <c r="J8" s="16" t="str">
         <f t="shared" si="1"/>
         <v>Low</v>
       </c>
       <c r="K8" s="6">
         <v>20000</v>
       </c>
-      <c r="L8" s="21">
+      <c r="L8" s="17">
         <v>0.1</v>
       </c>
       <c r="M8" s="6">
@@ -6001,15 +5991,15 @@
         <v>2000</v>
       </c>
       <c r="N8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B11" s="13">
         <f>SUMIFS(M4:M20,O4:O20,"Open")</f>
@@ -6027,7 +6017,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B13" s="13">
         <f>B11+B12</f>
@@ -6036,7 +6026,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B14" s="13">
         <f>'Change Log'!B11</f>
@@ -6045,7 +6035,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B15" s="13">
         <f>B14-B13</f>
@@ -6054,7 +6044,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B16">
         <f>COUNTIFS(J4:J20,"High",O4:O20,"Open")</f>
@@ -6096,8 +6086,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
-        <v>108</v>
+      <c r="A1" s="18" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -6111,7 +6101,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B4" s="6">
         <f>Budget!O10</f>
@@ -6120,7 +6110,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B5" s="13">
         <f>'Change Log'!B11</f>
@@ -6147,7 +6137,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B8" s="13">
         <f>'Change Log'!B13</f>
@@ -6156,7 +6146,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B9" s="13">
         <f>'Risk Register'!B13</f>
@@ -6165,7 +6155,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B10">
         <f>'Risk Register'!B16</f>
@@ -6174,7 +6164,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B11" t="str">
         <f>IF(B8&gt;=0,"Green",IF(B8/B5&gt;=-0.05,"Amber","Red"))</f>
@@ -6183,7 +6173,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C20" s="9">
         <f>Budget!C3</f>
@@ -6236,7 +6226,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C21" s="6">
         <f>Budget!C11</f>
@@ -6290,7 +6280,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C22" s="6">
         <f>Actuals!C11</f>
@@ -6345,7 +6335,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C23" s="6">
         <f>Forecast!C21</f>
